--- a/F3M_Finanzas_Estrategicas_assessment_ready_AI_v0.xlsx
+++ b/F3M_Finanzas_Estrategicas_assessment_ready_AI_v0.xlsx
@@ -131,10 +131,10 @@
     <t>Visión financiera integrada con modelo operativo, capacidades, tecnología, datos, talento, KPIs y roadmap de transformación.</t>
   </si>
   <si>
-    <t>Visión financiera dinámica y AI-enabled, con actualización basada en señales internas/externas, escenarios, salud financiera y recomendaciones estratégicas.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; Generate investing strategies from consolidated market conditions, internal financial performance, and firm objectives; Next-level market intelligence</t>
+    <t>Visión financiera dinámica y basada en IA, con actualización basada en señales internas/externas, escenarios, salud financiera y recomendaciones estratégicas.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; Generación de estrategias de inversión a partir de las condiciones de mercado consolidadas, el rendimiento financiero interno y los objetivos de la firma; Inteligencia de mercado de nueva generación</t>
   </si>
   <si>
     <t>¿Existe una visión financiera formal?
@@ -167,10 +167,10 @@
     <t>Capital allocation integrado con planificación estratégica, portfolio, business cases, escenarios, recursos y revisión periódica de retorno.</t>
   </si>
   <si>
-    <t>Modelo AI-enabled de asignación dinámica de capital, con simulación de escenarios, recomendaciones de inversión/desinversión y aprendizaje sobre retornos reales.</t>
-  </si>
-  <si>
-    <t>Generate investing strategies from consolidated market conditions, internal financial performance, and firm objectives; Predictive company valuation analyzing financial data; Project-level recommendations</t>
+    <t>Modelo basado en IA de asignación dinámica de capital, con simulación de escenarios, recomendaciones de inversión/desinversión y aprendizaje sobre retornos reales.</t>
+  </si>
+  <si>
+    <t>Generación de estrategias de inversión a partir de las condiciones de mercado consolidadas, el rendimiento financiero interno y los objetivos de la firma; Valoración predictiva de la compañía a partir del análisis de datos financieros; Recomendaciones a nivel de proyecto</t>
   </si>
   <si>
     <t>¿Existen criterios homogéneos de asignación de capital?
@@ -203,10 +203,10 @@
     <t>Market intelligence integrado con planificación, escenarios, riesgos, capital allocation y performance management.</t>
   </si>
   <si>
-    <t>AI monitoriza fuentes internas/externas, sintetiza señales de mercado, identifica implicaciones financieras y recomienda acciones estratégicas.</t>
-  </si>
-  <si>
-    <t>Next-level market intelligence; Generate investing strategies from consolidated market conditions; Smarter intelligence</t>
+    <t>IA monitoriza fuentes internas/externas, sintetiza señales de mercado, identifica implicaciones financieras y recomienda acciones estratégicas.</t>
+  </si>
+  <si>
+    <t>Inteligencia de mercado de nueva generación; Generación de estrategias de inversión a partir de las condiciones de mercado consolidadas; Inteligencia más avanzada</t>
   </si>
   <si>
     <t>¿Se integran señales de mercado en la visión financiera?
@@ -239,10 +239,10 @@
     <t>Monitorización integrada de salud financiera con escenarios, riesgos, oportunidades, acciones y seguimiento de impacto.</t>
   </si>
   <si>
-    <t>Executive financial health overview AI-enabled, con alertas tempranas, explicación automática de drivers y recomendaciones para dirección.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; FinanceAI Insights Platform; Identify past data patterns to predict and improve future financial performance</t>
+    <t>Executive financial health overview basado en IA, con alertas tempranas, explicación automática de drivers y recomendaciones para dirección.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
   </si>
   <si>
     <t>¿Existe cuadro de salud financiera?
@@ -278,10 +278,10 @@
     <t>Gobierno integrado de transformación con prioridades, recursos, dependencias, riesgos, beneficios y reporting ejecutivo del avance.</t>
   </si>
   <si>
-    <t>Transformation office AI-enabled, con priorización dinámica, recomendación de acciones, detección de riesgos y simulación de impacto del portfolio.</t>
-  </si>
-  <si>
-    <t>Project-level recommendations; Code assistant for digital transformation; FinanceAI Insights Platform</t>
+    <t>Transformation office basado en IA, con priorización dinámica, recomendación de acciones, detección de riesgos y simulación de impacto del portfolio.</t>
+  </si>
+  <si>
+    <t>Recomendaciones a nivel de proyecto; Asistente de código para la transformación digital; FinanceAI Insights Platform</t>
   </si>
   <si>
     <t>¿Existe roadmap de transformación financiera?
@@ -314,10 +314,10 @@
     <t>Modelo operativo integrado con tecnología, datos, talento, centros de excelencia, business partnering y mejora continua.</t>
   </si>
   <si>
-    <t>Modelo operativo adaptable y AI-enabled, con automatización de tareas, reasignación dinámica de capacidad y roles orientados a análisis, control y valor.</t>
-  </si>
-  <si>
-    <t>Code assistant for digital transformation; AI agents for software engineering; Automate financial data across diverse sources</t>
+    <t>Modelo operativo adaptable y basado en IA, con automatización de tareas, reasignación dinámica de capacidad y roles orientados a análisis, control y valor.</t>
+  </si>
+  <si>
+    <t>Asistente de código para la transformación digital; Agentes de IA para ingeniería de software; Automatización de datos financieros de fuentes diversas</t>
   </si>
   <si>
     <t>¿Está definido el modelo operativo financiero?
@@ -350,10 +350,10 @@
     <t>Plataforma integrada de datos y automatización, con gobierno de datos, estándares, autoservicio, controles y medición de beneficios.</t>
   </si>
   <si>
-    <t>Finance digital backbone AI-enabled, con automatización inteligente, agentes, copilots, analítica avanzada y recomendaciones proactivas.</t>
-  </si>
-  <si>
-    <t>Code assistant for digital transformation; AI agents for software engineering; Enterprise-wide data search and access; Data access for all</t>
+    <t>Finance digital backbone basado en IA, con automatización inteligente, agentes, copilots, analítica avanzada y recomendaciones proactivas.</t>
+  </si>
+  <si>
+    <t>Asistente de código para la transformación digital; Agentes de IA para ingeniería de software; Búsqueda y acceso a datos en toda la compañía; Acceso a datos para toda la organización</t>
   </si>
   <si>
     <t>¿Existe roadmap digital de Finanzas?
@@ -365,7 +365,7 @@
     <t>Arquitectura objetivo; roadmap digital; catálogo de automatizaciones; data governance; modelos de datos; KPIs de automatización; business cases.</t>
   </si>
   <si>
-    <t>Construir roadmap digital de Finanzas con arquitectura, datos, automatización, AI use cases, gobierno y medición de beneficios.</t>
+    <t>Construir roadmap digital de Finanzas con arquitectura, datos, automatización, casos de uso de IA, gobierno y medición de beneficios.</t>
   </si>
   <si>
     <t>2.4 Gestión del cambio, adopción y capacidades digitales</t>
@@ -386,10 +386,10 @@
     <t>Gestión del cambio integrada con roadmap, liderazgo, capacidades digitales, redes de champions y medición de adopción/valor.</t>
   </si>
   <si>
-    <t>AI apoya adopción y aprendizaje personalizado, detecta barreras de cambio, recomienda intervenciones y mide uso/impacto de nuevas capacidades.</t>
-  </si>
-  <si>
-    <t>AI-powered archive access and extraction; Enterprise-wide data search and access; Code assistant for digital transformation</t>
+    <t>IA apoya adopción y aprendizaje personalizado, detecta barreras de cambio, recomienda intervenciones y mide uso/impacto de nuevas capacidades.</t>
+  </si>
+  <si>
+    <t>Acceso y extracción documental impulsados por IA; Búsqueda y acceso a datos en toda la compañía; Asistente de código para la transformación digital</t>
   </si>
   <si>
     <t>¿Existe plan de gestión del cambio?
@@ -425,10 +425,10 @@
     <t>Finanzas co-lidera transformaciones críticas, integrando valor, recursos, riesgos, dependencias, beneficios y decisiones de portfolio.</t>
   </si>
   <si>
-    <t>Finance as strategic transformation partner, con AI para identificar oportunidades, riesgos, impactos, dependencias y recomendaciones de acción.</t>
-  </si>
-  <si>
-    <t>Project-level recommendations; Recommend, summarize, and detect risk from M&amp;A cleanroom data; Generate executive level overview of company financial health</t>
+    <t>Finance as strategic transformation partner, con IA para identificar oportunidades, riesgos, impactos, dependencias y recomendaciones de acción.</t>
+  </si>
+  <si>
+    <t>Recomendaciones a nivel de proyecto; Recomendación, resumen y detección de riesgos a partir de los datos del clean room de M&amp;A; Generación de una visión ejecutiva de la salud financiera de la compañía</t>
   </si>
   <si>
     <t>¿Finanzas participa desde fases tempranas?
@@ -461,10 +461,10 @@
     <t>Portfolio integrado con planificación financiera, recursos, roadmap, beneficios, escenarios y revisión periódica de prioridades.</t>
   </si>
   <si>
-    <t>AI recomienda priorización del portfolio, detecta dependencias y riesgos, simula escenarios de ejecución y propone reasignación de recursos.</t>
-  </si>
-  <si>
-    <t>Project-level recommendations; Summarize and score project proposals across the organization; Identify past data patterns to predict and improve future financial performance</t>
+    <t>IA recomienda priorización del portfolio, detecta dependencias y riesgos, simula escenarios de ejecución y propone reasignación de recursos.</t>
+  </si>
+  <si>
+    <t>Recomendaciones a nivel de proyecto; Resumen y puntuación de propuestas de proyecto en toda la organización; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
   </si>
   <si>
     <t>¿Existe portfolio consolidado de iniciativas?
@@ -497,10 +497,10 @@
     <t>Gestión integrada de decisiones corporativas con due diligence, clean room, integración, sinergias, riesgos, beneficios y governance post-deal.</t>
   </si>
   <si>
-    <t>AI analiza información de clean room, resume riesgos, identifica sinergias, modeliza escenarios y recomienda focos de decisión/integración.</t>
-  </si>
-  <si>
-    <t>Recommend, summarize, and detect risk from M&amp;A cleanroom data; Predictive company valuation analyzing financial data; Generate investing strategies</t>
+    <t>IA analiza información de clean room, resume riesgos, identifica sinergias, modeliza escenarios y recomienda focos de decisión/integración.</t>
+  </si>
+  <si>
+    <t>Recomendación, resumen y detección de riesgos a partir de los datos del clean room de M&amp;A; Valoración predictiva de la compañía a partir del análisis de datos financieros; Generación de estrategias de inversión</t>
   </si>
   <si>
     <t>¿Existe metodología financiera para M&amp;A/integración?
@@ -533,10 +533,10 @@
     <t>Gestión integrada de valor con estrategia, portfolio, forecast, acciones correctivas, aprendizaje y decisiones de reasignación.</t>
   </si>
   <si>
-    <t>AI compara beneficios esperados/reales, detecta patrones de captura de valor, recomienda acciones y retroalimenta futuros business cases.</t>
-  </si>
-  <si>
-    <t>Project-level recommendations; Generate executive level overview of company financial health; FinanceAI Insights Platform</t>
+    <t>IA compara beneficios esperados/reales, detecta patrones de captura de valor, recomienda acciones y retroalimenta futuros business cases.</t>
+  </si>
+  <si>
+    <t>Recomendaciones a nivel de proyecto; Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform</t>
   </si>
   <si>
     <t>¿Se miden beneficios reales vs esperados?

--- a/F3M_Finanzas_Estrategicas_assessment_ready_AI_v0.xlsx
+++ b/F3M_Finanzas_Estrategicas_assessment_ready_AI_v0.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="222">
   <si>
     <t>Capacidad</t>
   </si>
@@ -724,6 +724,42 @@
   </si>
   <si>
     <t>Evaluar situación actual, sustentar el score con evidencias, separar las tres palancas, validar resultados con responsables del dominio y preservar la conexión entre visión, transformación y valor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Generación de estrategias de inversión; Inteligencia de mercado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de estrategias de inversión; Valoración predictiva de la compañía; Recomendaciones de acción a nivel de proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inteligencia de mercado; Generación de estrategias de inversión; Síntesis multifuente para informes de análisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Analista digital de Finanzas bajo demanda; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de acción a nivel de proyecto; Asistente de código para la transformación; Analista digital de Finanzas bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente de código para la transformación; Agentes de IA para ingeniería de software; Integración automatizada de datos financieros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente de código para la transformación; Agentes de IA para ingeniería de software; Consulta del dato en lenguaje natural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceso y extracción documental; Consulta del dato en lenguaje natural; Asistente de código para la transformación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de acción a nivel de proyecto; Análisis del clean room de M&amp;A; Visión ejecutiva de la salud financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de acción a nivel de proyecto; Resumen y puntuación de propuestas de inversión; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis del clean room de M&amp;A; Valoración predictiva de la compañía; Generación de estrategias de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de acción a nivel de proyecto; Visión ejecutiva de la salud financiera; Analista digital de Finanzas bajo demanda</t>
   </si>
 </sst>
 </file>
@@ -1467,7 +1503,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1525,7 +1561,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1583,7 +1619,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1641,7 +1677,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1699,7 +1735,7 @@
         <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1757,7 +1793,7 @@
         <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1815,7 +1851,7 @@
         <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1873,7 +1909,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1931,7 +1967,7 @@
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1989,7 +2025,7 @@
         <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2047,7 +2083,7 @@
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2105,7 +2141,7 @@
         <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2849,7 +2885,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G13" si="0">IF(C2="","",IF(C2&gt;=3,"Oleada 1",IF(C2=2,"Oleada 2",IF(C2=1,"Oleada 3",""))))</f>
@@ -2880,7 +2916,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2911,7 +2947,7 @@
         <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2942,7 +2978,7 @@
         <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2973,7 +3009,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3004,7 +3040,7 @@
         <v>87</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3035,7 +3071,7 @@
         <v>98</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3066,7 +3102,7 @@
         <v>109</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3097,7 +3133,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3128,7 +3164,7 @@
         <v>132</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3159,7 +3195,7 @@
         <v>143</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3190,7 +3226,7 @@
         <v>154</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3250,7 +3286,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -3267,7 +3303,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -3284,7 +3320,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>49</v>
@@ -3301,7 +3337,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>60</v>
@@ -3318,7 +3354,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -3335,7 +3371,7 @@
         <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>83</v>
@@ -3352,7 +3388,7 @@
         <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
@@ -3369,7 +3405,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>105</v>
@@ -3386,7 +3422,7 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>117</v>
@@ -3403,7 +3439,7 @@
         <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>128</v>
@@ -3420,7 +3456,7 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>139</v>
@@ -3437,7 +3473,7 @@
         <v>144</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>150</v>

--- a/F3M_Finanzas_Estrategicas_assessment_ready_AI_v0.xlsx
+++ b/F3M_Finanzas_Estrategicas_assessment_ready_AI_v0.xlsx
@@ -239,7 +239,7 @@
     <t>Monitorización integrada de salud financiera con escenarios, riesgos, oportunidades, acciones y seguimiento de impacto.</t>
   </si>
   <si>
-    <t>Executive financial health overview basado en IA, con alertas tempranas, explicación automática de drivers y recomendaciones para dirección.</t>
+    <t>Panorámica ejecutiva de la salud financiera basada en IA, con alertas tempranas, explicación automática de los drivers y recomendaciones para la dirección.</t>
   </si>
   <si>
     <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
@@ -278,7 +278,7 @@
     <t>Gobierno integrado de transformación con prioridades, recursos, dependencias, riesgos, beneficios y reporting ejecutivo del avance.</t>
   </si>
   <si>
-    <t>Transformation office basado en IA, con priorización dinámica, recomendación de acciones, detección de riesgos y simulación de impacto del portfolio.</t>
+    <t>Oficina de transformación apoyada en IA, con priorización dinámica, recomendación de acciones, detección de riesgos y simulación del impacto de la cartera de iniciativas.</t>
   </si>
   <si>
     <t>Recomendaciones a nivel de proyecto; Asistente de código para la transformación digital; FinanceAI Insights Platform</t>
@@ -350,7 +350,7 @@
     <t>Plataforma integrada de datos y automatización, con gobierno de datos, estándares, autoservicio, controles y medición de beneficios.</t>
   </si>
   <si>
-    <t>Finance digital backbone basado en IA, con automatización inteligente, agentes, copilots, analítica avanzada y recomendaciones proactivas.</t>
+    <t>Columna vertebral digital de Finanzas basada en IA, con automatización inteligente, agentes, asistentes, analítica avanzada y recomendaciones proactivas.</t>
   </si>
   <si>
     <t>Asistente de código para la transformación digital; Agentes de IA para ingeniería de software; Búsqueda y acceso a datos en toda la compañía; Acceso a datos para toda la organización</t>
@@ -425,7 +425,7 @@
     <t>Finanzas co-lidera transformaciones críticas, integrando valor, recursos, riesgos, dependencias, beneficios y decisiones de portfolio.</t>
   </si>
   <si>
-    <t>Finance as strategic transformation partner, con IA para identificar oportunidades, riesgos, impactos, dependencias y recomendaciones de acción.</t>
+    <t>Finanzas como socio estratégico de la transformación, con IA para identificar oportunidades, riesgos, impactos, dependencias y acciones recomendadas.</t>
   </si>
   <si>
     <t>Recomendaciones a nivel de proyecto; Recomendación, resumen y detección de riesgos a partir de los datos del clean room de M&amp;A; Generación de una visión ejecutiva de la salud financiera de la compañía</t>
@@ -461,7 +461,7 @@
     <t>Portfolio integrado con planificación financiera, recursos, roadmap, beneficios, escenarios y revisión periódica de prioridades.</t>
   </si>
   <si>
-    <t>IA recomienda priorización del portfolio, detecta dependencias y riesgos, simula escenarios de ejecución y propone reasignación de recursos.</t>
+    <t>La IA recomienda la priorización de la cartera de iniciativas, detecta dependencias y riesgos, simula escenarios de ejecución y propone la reasignación de recursos.</t>
   </si>
   <si>
     <t>Recomendaciones a nivel de proyecto; Resumen y puntuación de propuestas de proyecto en toda la organización; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>

--- a/F3M_Finanzas_Estrategicas_assessment_ready_AI_v0.xlsx
+++ b/F3M_Finanzas_Estrategicas_assessment_ready_AI_v0.xlsx
@@ -146,7 +146,7 @@
     <t>Documento de visión financiera; estrategia corporativa; prioridades del CFO; roadmap; KPIs; presentaciones a comité; entrevistas con stakeholders.</t>
   </si>
   <si>
-    <t>Definir o actualizar la visión financiera corporativa con narrativa estratégica, prioridades, capacidades objetivo, KPIs y roadmap asociado.</t>
+    <t>Definir o actualizar la visión financiera corporativa con narrativa estratégica, prioridades, capacidades objetivo, KPIs y hoja de ruta asociada.</t>
   </si>
   <si>
     <t>1.2 Modelo de creación de valor y capital allocation</t>
@@ -182,7 +182,7 @@
     <t>Política de capital allocation; portfolio de inversiones; business cases; actas de comité; benefit tracking; escenarios; decisiones de reasignación.</t>
   </si>
   <si>
-    <t>Diseñar modelo de capital allocation con criterios de valor/riesgo, escenarios, seguimiento de beneficios y revisión dinámica del portfolio.</t>
+    <t>Diseñar modelo de asignación de capital con criterios de valor y riesgo, escenarios, seguimiento de beneficios y revisión dinámica de la cartera.</t>
   </si>
   <si>
     <t>1.3 Inteligencia de mercado, competitiva y financiera</t>
@@ -218,7 +218,7 @@
     <t>Informes de mercado; benchmarks; análisis de competidores; dashboards externos; actas de comité; escenarios macro/sectoriales.</t>
   </si>
   <si>
-    <t>Crear modelo de financial market intelligence con fuentes, benchmarks, señales externas, implicaciones financieras y rutina ejecutiva.</t>
+    <t>Crear modelo de inteligencia de mercados financieros con fuentes, referencias de mercado, señales externas, implicaciones financieras y rutina ejecutiva.</t>
   </si>
   <si>
     <t>1.4 Gobierno de performance estratégica y salud financiera</t>
@@ -254,7 +254,7 @@
     <t>Cuadro de mando estratégico; KPIs; targets; actas de comité; análisis de desviaciones; planes de acción; alertas.</t>
   </si>
   <si>
-    <t>Implantar executive financial health dashboard con KPIs estratégicos, drivers, riesgos, alertas, owners y acciones de seguimiento.</t>
+    <t>Implantar cuadro de mando ejecutivo de salud financiera con KPIs estratégicos, drivers, riesgos, alertas, responsables y acciones de seguimiento.</t>
   </si>
   <si>
     <t>Transformación financiera</t>
@@ -293,7 +293,7 @@
     <t>Roadmap de transformación; portfolio de iniciativas; comité de transformación; KPIs; benefit tracker; matriz de dependencias; riesgos.</t>
   </si>
   <si>
-    <t>Definir modelo de gobierno de transformación financiera con portfolio, priorización, dependencias, beneficios, owners y reporting ejecutivo.</t>
+    <t>Definir modelo de gobierno de transformación financiera con cartera de iniciativas, priorización, dependencias, beneficios, responsables e informes a la dirección.</t>
   </si>
   <si>
     <t>2.2 Rediseño del modelo operativo financiero</t>
@@ -329,7 +329,7 @@
     <t>TOM financiero; RACI; mapa de procesos; catálogo de servicios; estructura organizativa; business partnering model; KPIs de productividad.</t>
   </si>
   <si>
-    <t>Diseñar target operating model financiero con servicios, roles, procesos, capacidades, tecnología, datos y métricas de productividad.</t>
+    <t>Diseñar el modelo operativo objetivo de Finanzas con servicios, roles, procesos, capacidades, tecnología, datos y métricas de productividad.</t>
   </si>
   <si>
     <t>2.3 Digitalización, datos y automatización de Finanzas</t>
@@ -365,7 +365,7 @@
     <t>Arquitectura objetivo; roadmap digital; catálogo de automatizaciones; data governance; modelos de datos; KPIs de automatización; business cases.</t>
   </si>
   <si>
-    <t>Construir roadmap digital de Finanzas con arquitectura, datos, automatización, casos de uso de IA, gobierno y medición de beneficios.</t>
+    <t>Construir hoja de ruta digital de Finanzas con arquitectura, datos, automatización, casos de uso de IA, gobierno y medición de beneficios.</t>
   </si>
   <si>
     <t>2.4 Gestión del cambio, adopción y capacidades digitales</t>
@@ -401,7 +401,7 @@
     <t>Plan de change; mapa de stakeholders; materiales de formación; métricas de adopción; encuestas; red de champions; comunicaciones.</t>
   </si>
   <si>
-    <t>Implantar modelo de gestión del cambio con stakeholders, formación, adopción, champions, métricas de uso y refuerzo de capacidades digitales.</t>
+    <t>Implantar modelo de gestión del cambio con grupos de interés, formación, adopción, referentes internos, métricas de uso y refuerzo de capacidades digitales.</t>
   </si>
   <si>
     <t>Transformación empresarial</t>
@@ -440,7 +440,7 @@
     <t>Portfolio de transformación; business cases; comités de transformación; roles de Finanzas; reportes de beneficios; decisiones de financiación.</t>
   </si>
   <si>
-    <t>Definir rol de Finanzas en transformación empresarial con governance, business case, funding, riesgos, beneficios y reporting de valor.</t>
+    <t>Definir el rol de Finanzas en la transformación empresarial con gobierno, business case, financiación, riesgos, beneficios e informes de valor.</t>
   </si>
   <si>
     <t>3.2 Gestión de portfolio de iniciativas estratégicas</t>
@@ -476,7 +476,7 @@
     <t>Portfolio estratégico; criterios de priorización; roadmap; matriz de dependencias; capacity planning; actas de comité; benefit tracker.</t>
   </si>
   <si>
-    <t>Implantar modelo de portfolio estratégico con priorización por valor, riesgo, capacidad, dependencias, escenarios y seguimiento de beneficios.</t>
+    <t>Implantar modelo de cartera estratégica con priorización por valor, riesgo, capacidad, dependencias, escenarios y seguimiento de beneficios.</t>
   </si>
   <si>
     <t>3.3 M&amp;A, integración y decisiones corporativas complejas</t>
@@ -512,7 +512,7 @@
     <t>Modelos de valoración; due diligence; clean room outputs; synergy tracker; integration plan; business case; post-deal review.</t>
   </si>
   <si>
-    <t>Diseñar metodología financiera para M&amp;A e integración con valoración, sinergias, riesgos, escenarios, governance y seguimiento post-deal.</t>
+    <t>Diseñar metodología financiera para M&amp;A e integración con valoración, sinergias, riesgos, escenarios, gobierno y seguimiento tras la operación.</t>
   </si>
   <si>
     <t>3.4 Seguimiento de beneficios, valor y aprendizaje empresarial</t>
@@ -548,7 +548,7 @@
     <t>Benefit tracker; líneas base; KPIs de valor; reportes de impacto; acciones correctivas; post-mortems; decisiones de portfolio.</t>
   </si>
   <si>
-    <t>Implantar modelo de value realization con línea base, owners, métricas, seguimiento, acciones correctivas y aprendizaje para futuros casos.</t>
+    <t>Implantar modelo de materialización del valor con línea base, responsables, métricas, seguimiento, acciones correctivas y aprendizaje para futuros casos.</t>
   </si>
   <si>
     <t>Score global dominio</t>
